--- a/SpreadSheets/GameBalance.xlsx
+++ b/SpreadSheets/GameBalance.xlsx
@@ -518,7 +518,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -578,7 +577,7 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>24</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>38</c:v>
@@ -782,7 +781,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -820,7 +818,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
@@ -834,7 +831,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -879,7 +875,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -936,7 +931,7 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>24</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>38</c:v>
@@ -1133,7 +1128,7 @@
                   <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>22</c:v>
@@ -1197,7 +1192,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1235,7 +1229,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
@@ -1249,7 +1242,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -1673,7 +1665,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="5">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" s="5">
         <v>56</v>
@@ -1683,7 +1675,7 @@
       </c>
       <c r="F5" s="7">
         <f t="shared" ref="F5:F20" si="0">D5-C5</f>
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>12</v>
@@ -1814,7 +1806,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" s="11">
         <f t="shared" si="0"/>
@@ -2158,7 +2150,7 @@
       <c r="D25" s="15"/>
       <c r="E25" s="16">
         <f>FLOOR(E17/E10, 1)</f>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F25" s="15"/>
       <c r="G25" s="17" t="s">
@@ -2178,8 +2170,7 @@
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
       <c r="E26" s="16">
-        <f>E19+E20</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="17" t="s">
